--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 18/08/2026, 14:46</x:t>
+    <x:t>Conta: 6445064 | 24/08/2026, 09:28</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>53,6%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 28.478.308,84</x:t>
+    <x:t>R$ 28.527.108,23</x:t>
   </x:si>
   <x:si>
     <x:t>4,90%|Prefixada</x:t>
@@ -91,10 +91,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.225,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.441,56</x:t>
+    <x:t>R$ 315.815,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.942,97</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2027</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 377.014,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 365.461,93</x:t>
+    <x:t>R$ 377.709,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 366.053,01</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -151,10 +151,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 254.656,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.458,44</x:t>
+    <x:t>R$ 255.153,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.880,60</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,00%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 312.473,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 303.102,71</x:t>
+    <x:t>R$ 313.036,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 303.580,92</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -178,10 +178,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.123,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.504,81</x:t>
+    <x:t>R$ 314.702,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.996,91</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -190,10 +190,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.023,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 303.569,68</x:t>
+    <x:t>R$ 313.591,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.052,50</x:t>
   </x:si>
   <x:si>
     <x:t>CDB STELLANTIS FINANCIAMENTOS - AGO/2026</x:t>
@@ -202,10 +202,10 @@
     <x:t>+12,28%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 376.815,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 365.293,47</x:t>
+    <x:t>R$ 377.509,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 365.882,87</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -217,10 +217,10 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 253.605,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 244.224,25</x:t>
+    <x:t>R$ 254.092,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 245.978,41</x:t>
   </x:si>
   <x:si>
     <x:t>45,40%|Pós-Fixada</x:t>
@@ -235,10 +235,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 269.129,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 257.031,73</x:t>
+    <x:t>R$ 269.780,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 259.313,54</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -262,7 +262,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.822.752,20</x:t>
+    <x:t>R$ 20.859.134,79</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 935.331,70</x:t>
+    <x:t>R$ 936.898,23</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -304,7 +304,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.000.707,55</x:t>
+    <x:t>R$ 1.002.383,57</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -313,7 +313,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.113.146,60</x:t>
+    <x:t>R$ 1.115.010,94</x:t>
   </x:si>
   <x:si>
     <x:t>3,10%|Inflação</x:t>
@@ -331,10 +331,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 433.949,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 421.357,47</x:t>
+    <x:t>R$ 434.425,85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 421.761,97</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -346,19 +346,19 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 443.479,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 429.457,62</x:t>
+    <x:t>R$ 444.043,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 429.937,11</x:t>
   </x:si>
   <x:si>
     <x:t>IPC-A +6,45%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 372.783,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 361.866,23</x:t>
+    <x:t>R$ 373.199,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 362.219,39</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PAN S/A - AGO/2026</x:t>
@@ -367,10 +367,10 @@
     <x:t>IPC-A +6,60%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 373.712,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 362.655,40</x:t>
+    <x:t>R$ 374.243,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 363.106,90</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -388,13 +388,13 @@
     <x:t>R$ 76.411,65</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 74.414,61</x:t>
+    <x:t>R$ 74.699,90</x:t>
   </x:si>
   <x:si>
     <x:t>45,2%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 24.025.566,19</x:t>
+    <x:t>R$ 24.073.321,05</x:t>
   </x:si>
   <x:si>
     <x:t>45,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -415,10 +415,10 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 560,56</x:t>
+    <x:t>24/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 562,01</x:t>
   </x:si>
   <x:si>
     <x:t>904,71</x:t>
@@ -427,31 +427,34 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 507.139,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 505.533,31</x:t>
+    <x:t>R$ 508.455,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.552,70</x:t>
   </x:si>
   <x:si>
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 271,47</x:t>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,02</x:t>
   </x:si>
   <x:si>
     <x:t>10.460,17</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.839.608,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.830.696,55</x:t>
+    <x:t>R$ 2.845.398,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.835.183,68</x:t>
   </x:si>
   <x:si>
     <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>14/08/2026</x:t>
+    <x:t>19/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 3,21</x:t>
@@ -460,25 +463,28 @@
     <x:t>246.820,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 792.947,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 792.127,51</x:t>
+    <x:t>R$ 793.200,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 792.343,02</x:t>
   </x:si>
   <x:si>
     <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 2,19</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 618.332,03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 604.428,91</x:t>
+    <x:t>R$ 619.773,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 605.654,47</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
@@ -490,100 +496,100 @@
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 191.336,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 190.572,75</x:t>
+    <x:t>R$ 191.400,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 190.626,96</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.790.940,78</x:t>
+    <x:t>R$ 4.800.144,85</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.701.780,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.559.489,27</x:t>
+    <x:t>R$ 4.710.813,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.567.167,13</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,16</x:t>
+    <x:t>R$ 2,17</x:t>
   </x:si>
   <x:si>
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 273.806,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 264.359,62</x:t>
+    <x:t>R$ 274.431,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 264.890,74</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 197,91</x:t>
+    <x:t>R$ 198,19</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.996.393,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.697.823,38</x:t>
+    <x:t>R$ 6.004.878,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.705.035,33</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 185,14</x:t>
+    <x:t>R$ 185,60</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.804.298,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.780.082,48</x:t>
+    <x:t>R$ 5.818.953,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.792.539,00</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 158,04</x:t>
+    <x:t>R$ 158,45</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 93.510,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 92.827,38</x:t>
+    <x:t>R$ 93.751,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.014,03</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,71</x:t>
+    <x:t>R$ 2,72</x:t>
   </x:si>
   <x:si>
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 176.413,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 170.321,28</x:t>
+    <x:t>R$ 176.938,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 170.768,25</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -595,16 +601,16 @@
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.029.998,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.023.248,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,91%|Fundos Imobiliários</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 483.936,00</x:t>
+    <x:t>R$ 2.035.325,51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.027.377,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,93%|Fundos Imobiliários</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 494.160,00</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -643,10 +649,10 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 16,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 85,20</x:t>
+    <x:t>-R$ 15,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 87,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,32%|Saldo projetado</x:t>
@@ -1290,10 +1296,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>53158816.6703955</x:v>
+        <x:v>53265594.9204782</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>52987811.0303955</x:v>
+        <x:v>53094589.2804782</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>171005.64</x:v>
@@ -2193,22 +2199,22 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C36" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G36" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2217,25 +2223,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C37" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G37" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2244,25 +2250,25 @@
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
       <x:c r="A38" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C38" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G38" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
       <x:c r="I38" s="3"/>
@@ -2271,25 +2277,25 @@
     </x:row>
     <x:row r="39" spans="1:11" ht="30" customHeight="1">
       <x:c r="A39" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C39" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G39" s="12" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H39" s="3"/>
       <x:c r="I39" s="3"/>
@@ -2298,25 +2304,25 @@
     </x:row>
     <x:row r="40" spans="1:11" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C40" s="12" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G40" s="12" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H40" s="3"/>
       <x:c r="I40" s="3"/>
@@ -2325,25 +2331,25 @@
     </x:row>
     <x:row r="41" spans="1:11" ht="30" customHeight="1">
       <x:c r="A41" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C41" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G41" s="12" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
@@ -2352,25 +2358,25 @@
     </x:row>
     <x:row r="42" spans="1:11" ht="30" customHeight="1">
       <x:c r="A42" s="12" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C42" s="12" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G42" s="12" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H42" s="3"/>
       <x:c r="I42" s="3"/>
@@ -2379,25 +2385,25 @@
     </x:row>
     <x:row r="43" spans="1:11" ht="30" customHeight="1">
       <x:c r="A43" s="12" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C43" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G43" s="12" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H43" s="3"/>
       <x:c r="I43" s="3"/>
@@ -2406,25 +2412,25 @@
     </x:row>
     <x:row r="44" spans="1:11" ht="30" customHeight="1">
       <x:c r="A44" s="12" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>133</x:v>
       </x:c>
       <x:c r="C44" s="12" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G44" s="12" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H44" s="3"/>
       <x:c r="I44" s="3"/>
@@ -2433,25 +2439,25 @@
     </x:row>
     <x:row r="45" spans="1:11" ht="30" customHeight="1">
       <x:c r="A45" s="12" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C45" s="12" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>188</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G45" s="12" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H45" s="3"/>
       <x:c r="I45" s="3"/>
@@ -2460,25 +2466,25 @@
     </x:row>
     <x:row r="46" spans="1:11" ht="30" customHeight="1">
       <x:c r="A46" s="13" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B46" s="13" t="s">
         <x:v>133</x:v>
       </x:c>
       <x:c r="C46" s="13" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D46" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E46" s="13" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F46" s="13" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G46" s="13" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H46" s="3"/>
       <x:c r="I46" s="3"/>
@@ -2500,7 +2506,7 @@
     </x:row>
     <x:row r="48" spans="1:11" ht="45" customHeight="1">
       <x:c r="A48" s="8" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B48" s="9"/>
       <x:c r="C48" s="9"/>
@@ -2512,7 +2518,7 @@
       <x:c r="I48" s="9"/>
       <x:c r="J48" s="9"/>
       <x:c r="K48" s="10" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2530,34 +2536,34 @@
     </x:row>
     <x:row r="50" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A50" s="11" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B50" s="11" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C50" s="11" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D50" s="11" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E50" s="11" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F50" s="11" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G50" s="11" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H50" s="11" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="I50" s="11" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="J50" s="11" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K50" s="11" t="s">
         <x:v>16</x:v>
@@ -2565,10 +2571,10 @@
     </x:row>
     <x:row r="51" spans="1:11" ht="30" customHeight="1">
       <x:c r="A51" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C51" s="13" t="s">
         <x:v>23</x:v>
@@ -2580,22 +2586,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F51" s="13" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G51" s="13" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H51" s="13" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="I51" s="13" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="J51" s="13" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K51" s="13" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
@@ -2613,7 +2619,7 @@
     </x:row>
     <x:row r="53" spans="1:11" ht="45" customHeight="1">
       <x:c r="A53" s="8" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B53" s="9"/>
       <x:c r="C53" s="9"/>
@@ -2625,7 +2631,7 @@
       <x:c r="I53" s="9"/>
       <x:c r="J53" s="9"/>
       <x:c r="K53" s="10" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
@@ -2649,66 +2655,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="11" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D55" s="11" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E55" s="11" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F55" s="11" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G55" s="11" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H55" s="11" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="I55" s="11" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="J55" s="11" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K55" s="11" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11" ht="30" customHeight="1">
       <x:c r="A56" s="13" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="J56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K56" s="13" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 24/08/2026, 09:28</x:t>
+    <x:t>Conta: 6445064 | 25/08/2026, 19:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>53,6%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 28.527.108,23</x:t>
+    <x:t>R$ 28.539.294,74</x:t>
   </x:si>
   <x:si>
     <x:t>4,90%|Prefixada</x:t>
@@ -91,10 +91,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.815,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.942,97</x:t>
+    <x:t>R$ 315.962,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.068,46</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2027</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 377.709,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 366.053,01</x:t>
+    <x:t>R$ 377.883,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 366.200,95</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -151,10 +151,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 255.153,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.880,60</x:t>
+    <x:t>R$ 255.277,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.986,27</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,00%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.036,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 303.580,92</x:t>
+    <x:t>R$ 313.177,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 303.700,61</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -178,10 +178,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.702,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.996,91</x:t>
+    <x:t>R$ 314.847,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.120,08</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -190,10 +190,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.591,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.052,50</x:t>
+    <x:t>R$ 313.733,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.173,35</x:t>
   </x:si>
   <x:si>
     <x:t>CDB STELLANTIS FINANCIAMENTOS - AGO/2026</x:t>
@@ -202,10 +202,10 @@
     <x:t>+12,28%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 377.509,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 365.882,87</x:t>
+    <x:t>R$ 377.682,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 366.030,40</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -217,10 +217,10 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 254.092,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 245.978,41</x:t>
+    <x:t>R$ 254.214,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.082,05</x:t>
   </x:si>
   <x:si>
     <x:t>45,40%|Pós-Fixada</x:t>
@@ -235,10 +235,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 269.780,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 259.313,54</x:t>
+    <x:t>R$ 269.943,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 259.452,14</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -262,7 +262,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.859.134,79</x:t>
+    <x:t>R$ 20.868.240,37</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 936.898,23</x:t>
+    <x:t>R$ 937.290,27</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -304,7 +304,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.002.383,57</x:t>
+    <x:t>R$ 1.002.803,02</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -313,7 +313,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.115.010,94</x:t>
+    <x:t>R$ 1.115.477,51</x:t>
   </x:si>
   <x:si>
     <x:t>3,10%|Inflação</x:t>
@@ -331,10 +331,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 434.425,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 421.761,97</x:t>
+    <x:t>R$ 434.544,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 421.863,17</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -346,19 +346,19 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 444.043,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 429.937,11</x:t>
+    <x:t>R$ 444.184,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 430.057,08</x:t>
   </x:si>
   <x:si>
     <x:t>IPC-A +6,45%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 373.199,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 362.219,39</x:t>
+    <x:t>R$ 373.303,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 362.307,74</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PAN S/A - AGO/2026</x:t>
@@ -367,10 +367,10 @@
     <x:t>IPC-A +6,60%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 374.243,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 363.106,90</x:t>
+    <x:t>R$ 374.349,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 363.197,28</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -394,7 +394,7 @@
     <x:t>45,2%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 24.073.321,05</x:t>
+    <x:t>R$ 24.064.578,72</x:t>
   </x:si>
   <x:si>
     <x:t>45,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -415,76 +415,76 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>25/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 562,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>904,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 508.726,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.763,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
     <x:t>24/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 562,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>904,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.455,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.552,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+    <x:t>R$ 272,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.460,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.846.790,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.836.262,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>246.820,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 793.471,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 792.572,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
     <x:t>21/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 272,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.460,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.845.398,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.835.183,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>246.820,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 793.200,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 792.343,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20/08/2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>R$ 2,19</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 619.773,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 605.654,47</x:t>
+    <x:t>R$ 620.140,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 605.965,85</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
@@ -496,25 +496,25 @@
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 191.400,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 190.626,96</x:t>
+    <x:t>R$ 191.768,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 190.939,51</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.800.144,85</x:t>
+    <x:t>R$ 4.800.755,61</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.710.813,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.567.167,13</x:t>
+    <x:t>R$ 4.711.413,03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.567.676,62</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
@@ -526,55 +526,55 @@
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 274.431,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 264.890,74</x:t>
+    <x:t>R$ 274.582,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 265.019,69</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 198,19</x:t>
+    <x:t>R$ 198,29</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.004.878,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.705.035,33</x:t>
+    <x:t>R$ 6.007.777,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.707.499,32</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 185,60</x:t>
+    <x:t>R$ 185,08</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.818.953,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.792.539,00</x:t>
+    <x:t>R$ 5.802.666,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.778.694,89</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 158,45</x:t>
+    <x:t>R$ 158,53</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 93.751,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.014,03</x:t>
+    <x:t>R$ 93.799,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.051,28</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
@@ -586,10 +586,10 @@
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 176.938,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 170.768,25</x:t>
+    <x:t>R$ 177.043,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 170.857,07</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -601,10 +601,10 @@
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.035.325,51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.027.377,28</x:t>
+    <x:t>R$ 2.036.399,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.028.209,83</x:t>
   </x:si>
   <x:si>
     <x:t>0,93%|Fundos Imobiliários</x:t>
@@ -1296,10 +1296,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>53265594.9204782</x:v>
+        <x:v>53269039.0991833</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>53094589.2804782</x:v>
+        <x:v>53098033.4591833</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>171005.64</x:v>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 25/08/2026, 19:18</x:t>
+    <x:t>Conta: 6445064 | 28/08/2026, 09:29</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>53,6%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 28.539.294,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,90%|Prefixada</x:t>
+    <x:t>52,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 27.132.847,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,70%|Prefixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,451 +70,403 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>CDB BANCO C6 CONSIGNADO S.A. - AGO/2026</x:t>
+    <x:t>CDB BANCO PLENO - AGO/2027</x:t>
   </x:si>
   <x:si>
     <x:t>27/08/2024</x:t>
   </x:si>
   <x:si>
+    <x:t>27/08/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+13,20%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 100.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 119.966,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 116.971,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB AGIBANK - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+12,31%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>300,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 300.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 378.406,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 366.645,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB NBC BANK - AGO/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+13,06%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 200.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 255.651,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 247.303,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+12,00%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>250,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 250.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 313.600,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.060,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/02/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+12,30%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 315.282,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.489,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+12,10%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 314.160,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.536,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+12,85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 254.580,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.393,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46,80%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB ORIGINAL - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/08/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 270.433,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 259.868,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCA BNDES - MAI/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/05/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/05/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/05/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.219,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 20.228.598,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 20.895.580,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCA BNDES - JUN/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/06/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/06/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 924.308,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 938.467,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCA BNDES - AGO/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/09/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/08/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 988.914,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.004.062,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.100.028,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.116.878,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,80%|Inflação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB BTG PACTUAL - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IPC-A +6,33%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>350,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 350.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 434.830,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.106,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LF BMG - AGO/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IPC-A +7,51%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 444.535,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 430.355,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDB BANCO PLENO - AGO/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IPC-A +7,40%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 65.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 76.411,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 74.699,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46,7%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 24.147.903,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNP Paribas Match FIF RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 563,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>904,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 509.519,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 507.377,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
     <x:t>27/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>+12,50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>250,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 250.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 315.962,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 306.068,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO PLENO - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/08/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+13,20%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 100.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 119.966,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 116.971,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB AGIBANK - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,31%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>300,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 300.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 377.883,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 366.200,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB NBC BANK - AGO/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+13,06%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 200.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 255.277,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.986,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,00%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 313.177,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 303.700,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/02/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,30%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 314.847,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.120,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,10%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 313.733,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.173,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB STELLANTIS FINANCIAMENTOS - AGO/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,28%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 377.682,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 366.030,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+12,85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 254.214,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.082,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,40%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB ORIGINAL - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/08/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>117,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 269.943,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 259.452,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LCA BNDES - MAI/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/05/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/05/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/05/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84,50% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.219,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 20.228.598,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 20.868.240,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LCA BNDES - JUN/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/06/2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/06/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 924.308,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 937.290,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LCA BNDES - AGO/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/09/2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/08/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 988.914,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.803,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.100.028,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.115.477,51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,10%|Inflação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BTG PACTUAL - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IPC-A +6,33%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>350,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 350.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 434.544,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 421.863,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LF BMG - AGO/2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IPC-A +7,51%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 444.184,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 430.057,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IPC-A +6,45%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 373.303,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 362.307,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO PAN S/A - AGO/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IPC-A +6,60%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 374.349,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 363.197,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDB BANCO PLENO - AGO/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IPC-A +7,40%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 65.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 76.411,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 74.699,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,2%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 24.064.578,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qtd. cotas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Em cotização</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNP Paribas Match FIF RF CP RL</x:t>
+    <x:t>R$ 272,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.460,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.851.231,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.839.704,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
     <x:t>25/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 562,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>904,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.726,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.763,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.460,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.846.790,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.836.262,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3,21</x:t>
+    <x:t>R$ 3,22</x:t>
   </x:si>
   <x:si>
     <x:t>246.820,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 793.471,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 792.572,98</x:t>
+    <x:t>R$ 794.481,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 793.431,85</x:t>
   </x:si>
   <x:si>
     <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,19</x:t>
+    <x:t>26/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2,20</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 620.140,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 605.965,85</x:t>
+    <x:t>R$ 621.241,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 606.901,71</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,90</x:t>
+    <x:t>R$ 1,91</x:t>
   </x:si>
   <x:si>
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 191.768,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 190.939,51</x:t>
+    <x:t>R$ 192.140,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 191.255,81</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.800.755,61</x:t>
+    <x:t>R$ 4.811.826,77</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.711.413,03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.567.676,62</x:t>
+    <x:t>R$ 4.722.278,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.576.911,97</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
@@ -526,55 +478,55 @@
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 274.582,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 265.019,69</x:t>
+    <x:t>R$ 275.057,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 265.423,38</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 198,29</x:t>
+    <x:t>R$ 198,54</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.007.777,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.707.499,32</x:t>
+    <x:t>R$ 6.015.463,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.714.032,39</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 185,08</x:t>
+    <x:t>R$ 186,77</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.802.666,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.778.694,89</x:t>
+    <x:t>R$ 5.855.566,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.823.659,80</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 158,53</x:t>
+    <x:t>R$ 158,77</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 93.799,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.051,28</x:t>
+    <x:t>R$ 93.943,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.162,66</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
@@ -586,10 +538,10 @@
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 177.043,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 170.857,07</x:t>
+    <x:t>R$ 177.359,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 171.125,92</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -601,16 +553,16 @@
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.036.399,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.028.209,83</x:t>
+    <x:t>R$ 2.039.621,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.030.706,45</x:t>
   </x:si>
   <x:si>
     <x:t>0,93%|Fundos Imobiliários</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 494.160,00</x:t>
+    <x:t>R$ 482.004,80</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -649,16 +601,10 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 15,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 87,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,32%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 171.005,64</x:t>
+    <x:t>-R$ 17,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 84,86</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -686,9 +632,6 @@
   </x:si>
   <x:si>
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>171005,64</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -1236,7 +1179,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K56"/>
+  <x:dimension ref="A1:K52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="51.853482" style="0" customWidth="1"/>
@@ -1296,13 +1239,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>53269039.0991833</x:v>
+        <x:v>51762756.1550205</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>53098033.4591833</x:v>
+        <x:v>51762756.1550205</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>171005.64</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1445,43 +1388,43 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="s">
+      <x:c r="F11" s="12" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="G11" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H11" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="s">
+      <x:c r="J11" s="12" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:11" ht="30" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="12" t="s">
         <x:v>35</x:v>
@@ -1511,55 +1454,55 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E13" s="12" t="s">
+      <x:c r="F13" s="12" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="G13" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H13" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="s">
+      <x:c r="J13" s="12" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="K13" s="3"/>
     </x:row>
     <x:row r="14" spans="1:11" ht="30" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="F14" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G14" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I14" s="12" t="s">
         <x:v>49</x:v>
@@ -1577,590 +1520,566 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G15" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12" t="s">
+      <x:c r="B16" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C16" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E16" s="12" t="s">
+      <x:c r="C16" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="s">
+      <x:c r="F16" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="s">
+      <x:c r="H16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="s">
+      <x:c r="J16" s="13" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12" t="s">
+    <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A17" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C17" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="s">
+      <x:c r="B17" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="12" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="s">
+      <x:c r="B18" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="s">
+      <x:c r="G18" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="s">
+      <x:c r="H18" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="13" t="s">
+      <x:c r="I18" s="12" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B18" s="13" t="s">
+      <x:c r="J18" s="12" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C18" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D18" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F18" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G18" s="13" t="s">
+      <x:c r="B19" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H18" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I18" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J18" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J19" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="H19" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="3"/>
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G20" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K20" s="3"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="E21" s="12" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="F21" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G21" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K21" s="3"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="13" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K21" s="3"/>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="12" t="s">
+      <x:c r="B22" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
+      <x:c r="D22" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E22" s="12" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="s">
+      <x:c r="E22" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="s">
+      <x:c r="G22" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H22" s="12" t="s">
+      <x:c r="H22" s="13" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="I22" s="12" t="s">
+      <x:c r="I22" s="13" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="s">
+      <x:c r="J22" s="13" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="K22" s="3"/>
     </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="12" t="s">
+    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A23" s="11" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C23" s="12" t="s">
+      <x:c r="B23" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="12" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="B24" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="s">
+      <x:c r="F24" s="12" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="s">
+      <x:c r="G24" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="s">
+      <x:c r="H24" s="12" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="s">
+      <x:c r="I24" s="12" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="K23" s="3"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D24" s="13" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
+      <x:c r="J24" s="12" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G24" s="13" t="s">
+      <x:c r="K24" s="3"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="12" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H24" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="I24" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="J24" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="K24" s="3"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A25" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="s">
+      <x:c r="H25" s="12" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="J26" s="13" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K26" s="3"/>
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A28" s="8" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="G28" s="10" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H28" s="3"/>
+      <x:c r="I28" s="3"/>
+      <x:c r="J28" s="3"/>
+      <x:c r="K28" s="3"/>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="3"/>
+      <x:c r="I29" s="3"/>
+      <x:c r="J29" s="3"/>
+      <x:c r="K29" s="3"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A30" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J25" s="11" t="s">
+      <x:c r="G30" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K25" s="3"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="12" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B26" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C26" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E26" s="12" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F26" s="12" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G26" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H26" s="12" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="I26" s="12" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="J26" s="12" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="K26" s="3"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A27" s="12" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B27" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C27" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E27" s="12" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F27" s="12" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H27" s="12" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="I27" s="12" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J27" s="12" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="K27" s="3"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A28" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B28" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C28" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E28" s="12" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F28" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G28" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H28" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I28" s="12" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="J28" s="12" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="K28" s="3"/>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A29" s="12" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B29" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C29" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="s">
+      <x:c r="H30" s="3"/>
+      <x:c r="I30" s="3"/>
+      <x:c r="J30" s="3"/>
+      <x:c r="K30" s="3"/>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A31" s="12" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F29" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I29" s="12" t="s">
+      <x:c r="B31" s="12" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="J29" s="12" t="s">
+      <x:c r="C31" s="12" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K29" s="3"/>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A30" s="13" t="s">
+      <x:c r="D31" s="12" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B30" s="13" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C30" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D30" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E30" s="13" t="s">
+      <x:c r="E31" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="F30" s="13" t="s">
+      <x:c r="F31" s="12" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G30" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H30" s="13" t="s">
+      <x:c r="G31" s="12" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="I30" s="13" t="s">
+      <x:c r="H31" s="3"/>
+      <x:c r="I31" s="3"/>
+      <x:c r="J31" s="3"/>
+      <x:c r="K31" s="3"/>
+    </x:row>
+    <x:row r="32" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A32" s="12" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="J30" s="13" t="s">
+      <x:c r="B32" s="12" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="K30" s="3"/>
-    </x:row>
-    <x:row r="31" spans="1:11">
-      <x:c r="A31" s="4"/>
-      <x:c r="B31" s="4"/>
-      <x:c r="C31" s="4"/>
-      <x:c r="D31" s="4"/>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
-      <x:c r="H31" s="4"/>
-      <x:c r="I31" s="4"/>
-      <x:c r="J31" s="4"/>
-      <x:c r="K31" s="4"/>
-    </x:row>
-    <x:row r="32" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A32" s="8" t="s">
+      <x:c r="C32" s="12" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B32" s="9"/>
-      <x:c r="C32" s="9"/>
-      <x:c r="D32" s="9"/>
-      <x:c r="E32" s="9"/>
-      <x:c r="F32" s="9"/>
-      <x:c r="G32" s="10" t="s">
+      <x:c r="D32" s="12" t="s">
         <x:v>126</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H32" s="3"/>
       <x:c r="I32" s="3"/>
       <x:c r="J32" s="3"/>
       <x:c r="K32" s="3"/>
     </x:row>
-    <x:row r="33" spans="1:11">
-      <x:c r="A33" s="4"/>
-      <x:c r="B33" s="4"/>
-      <x:c r="C33" s="4"/>
-      <x:c r="D33" s="4"/>
-      <x:c r="E33" s="4"/>
-      <x:c r="F33" s="4"/>
-      <x:c r="G33" s="4"/>
+    <x:row r="33" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A33" s="12" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="s">
+        <x:v>134</x:v>
+      </x:c>
       <x:c r="H33" s="3"/>
       <x:c r="I33" s="3"/>
       <x:c r="J33" s="3"/>
       <x:c r="K33" s="3"/>
     </x:row>
-    <x:row r="34" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A34" s="11" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G34" s="11" t="s">
-        <x:v>17</x:v>
+    <x:row r="34" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A34" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="s">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H34" s="3"/>
       <x:c r="I34" s="3"/>
@@ -2169,25 +2088,25 @@
     </x:row>
     <x:row r="35" spans="1:11" ht="30" customHeight="1">
       <x:c r="A35" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C35" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
-        <x:v>137</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G35" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H35" s="3"/>
       <x:c r="I35" s="3"/>
@@ -2196,25 +2115,25 @@
     </x:row>
     <x:row r="36" spans="1:11" ht="30" customHeight="1">
       <x:c r="A36" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C36" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G36" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2223,25 +2142,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C37" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G37" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2250,25 +2169,25 @@
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
       <x:c r="A38" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C38" s="12" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G38" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
       <x:c r="I38" s="3"/>
@@ -2277,25 +2196,25 @@
     </x:row>
     <x:row r="39" spans="1:11" ht="30" customHeight="1">
       <x:c r="A39" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C39" s="12" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G39" s="12" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H39" s="3"/>
       <x:c r="I39" s="3"/>
@@ -2304,25 +2223,25 @@
     </x:row>
     <x:row r="40" spans="1:11" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C40" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G40" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H40" s="3"/>
       <x:c r="I40" s="3"/>
@@ -2331,25 +2250,25 @@
     </x:row>
     <x:row r="41" spans="1:11" ht="30" customHeight="1">
       <x:c r="A41" s="12" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="12" t="s">
-        <x:v>168</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>169</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G41" s="12" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
@@ -2357,364 +2276,256 @@
       <x:c r="K41" s="3"/>
     </x:row>
     <x:row r="42" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A42" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B42" s="12" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C42" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D42" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="E42" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F42" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G42" s="12" t="s">
+      <x:c r="A42" s="13" t="s">
         <x:v>176</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D42" s="13" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="s">
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H42" s="3"/>
       <x:c r="I42" s="3"/>
       <x:c r="J42" s="3"/>
       <x:c r="K42" s="3"/>
     </x:row>
-    <x:row r="43" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A43" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="B43" s="12" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C43" s="12" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D43" s="12" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E43" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F43" s="12" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G43" s="12" t="s">
+    <x:row r="43" spans="1:11">
+      <x:c r="A43" s="4"/>
+      <x:c r="B43" s="4"/>
+      <x:c r="C43" s="4"/>
+      <x:c r="D43" s="4"/>
+      <x:c r="E43" s="4"/>
+      <x:c r="F43" s="4"/>
+      <x:c r="G43" s="4"/>
+      <x:c r="H43" s="4"/>
+      <x:c r="I43" s="4"/>
+      <x:c r="J43" s="4"/>
+      <x:c r="K43" s="4"/>
+    </x:row>
+    <x:row r="44" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A44" s="8" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H43" s="3"/>
-      <x:c r="I43" s="3"/>
-      <x:c r="J43" s="3"/>
-      <x:c r="K43" s="3"/>
-    </x:row>
-    <x:row r="44" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A44" s="12" t="s">
+      <x:c r="B44" s="9"/>
+      <x:c r="C44" s="9"/>
+      <x:c r="D44" s="9"/>
+      <x:c r="E44" s="9"/>
+      <x:c r="F44" s="9"/>
+      <x:c r="G44" s="9"/>
+      <x:c r="H44" s="9"/>
+      <x:c r="I44" s="9"/>
+      <x:c r="J44" s="9"/>
+      <x:c r="K44" s="10" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="B44" s="12" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C44" s="12" t="s">
+    </x:row>
+    <x:row r="45" spans="1:11">
+      <x:c r="A45" s="4"/>
+      <x:c r="B45" s="4"/>
+      <x:c r="C45" s="4"/>
+      <x:c r="D45" s="4"/>
+      <x:c r="E45" s="4"/>
+      <x:c r="F45" s="4"/>
+      <x:c r="G45" s="4"/>
+      <x:c r="H45" s="4"/>
+      <x:c r="I45" s="4"/>
+      <x:c r="J45" s="4"/>
+      <x:c r="K45" s="4"/>
+    </x:row>
+    <x:row r="46" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A46" s="11" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D44" s="12" t="s">
+      <x:c r="B46" s="11" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="E44" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F44" s="12" t="s">
+      <x:c r="C46" s="11" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G44" s="12" t="s">
+      <x:c r="D46" s="11" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H44" s="3"/>
-      <x:c r="I44" s="3"/>
-      <x:c r="J44" s="3"/>
-      <x:c r="K44" s="3"/>
-    </x:row>
-    <x:row r="45" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A45" s="12" t="s">
+      <x:c r="E46" s="11" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="B45" s="12" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C45" s="12" t="s">
+      <x:c r="F46" s="11" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="D45" s="12" t="s">
+      <x:c r="G46" s="11" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="E45" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F45" s="12" t="s">
+      <x:c r="H46" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G45" s="12" t="s">
+      <x:c r="J46" s="11" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="H45" s="3"/>
-      <x:c r="I45" s="3"/>
-      <x:c r="J45" s="3"/>
-      <x:c r="K45" s="3"/>
-    </x:row>
-    <x:row r="46" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A46" s="13" t="s">
+      <x:c r="K46" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A47" s="13" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B46" s="13" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C46" s="13" t="s">
+      <x:c r="B47" s="13" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D46" s="13" t="s">
+      <x:c r="C47" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D47" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E47" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F47" s="13" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G47" s="13" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="E46" s="13" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F46" s="13" t="s">
+      <x:c r="H47" s="13" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="I47" s="13" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G46" s="13" t="s">
+      <x:c r="J47" s="13" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H46" s="3"/>
-      <x:c r="I46" s="3"/>
-      <x:c r="J46" s="3"/>
-      <x:c r="K46" s="3"/>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="A47" s="4"/>
-      <x:c r="B47" s="4"/>
-      <x:c r="C47" s="4"/>
-      <x:c r="D47" s="4"/>
-      <x:c r="E47" s="4"/>
-      <x:c r="F47" s="4"/>
-      <x:c r="G47" s="4"/>
-      <x:c r="H47" s="4"/>
-      <x:c r="I47" s="4"/>
-      <x:c r="J47" s="4"/>
-      <x:c r="K47" s="4"/>
-    </x:row>
-    <x:row r="48" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A48" s="8" t="s">
+      <x:c r="K47" s="13" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:11">
+      <x:c r="A48" s="4"/>
+      <x:c r="B48" s="4"/>
+      <x:c r="C48" s="4"/>
+      <x:c r="D48" s="4"/>
+      <x:c r="E48" s="4"/>
+      <x:c r="F48" s="4"/>
+      <x:c r="G48" s="4"/>
+      <x:c r="H48" s="4"/>
+      <x:c r="I48" s="4"/>
+      <x:c r="J48" s="4"/>
+      <x:c r="K48" s="4"/>
+    </x:row>
+    <x:row r="49" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A49" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B49" s="9"/>
+      <x:c r="C49" s="9"/>
+      <x:c r="D49" s="9"/>
+      <x:c r="E49" s="9"/>
+      <x:c r="F49" s="9"/>
+      <x:c r="G49" s="9"/>
+      <x:c r="H49" s="9"/>
+      <x:c r="I49" s="9"/>
+      <x:c r="J49" s="9"/>
+      <x:c r="K49" s="10" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:11">
+      <x:c r="A50" s="4"/>
+      <x:c r="B50" s="4"/>
+      <x:c r="C50" s="4"/>
+      <x:c r="D50" s="4"/>
+      <x:c r="E50" s="4"/>
+      <x:c r="F50" s="4"/>
+      <x:c r="G50" s="4"/>
+      <x:c r="H50" s="4"/>
+      <x:c r="I50" s="4"/>
+      <x:c r="J50" s="4"/>
+      <x:c r="K50" s="4"/>
+    </x:row>
+    <x:row r="51" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A51" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B48" s="9"/>
-      <x:c r="C48" s="9"/>
-      <x:c r="D48" s="9"/>
-      <x:c r="E48" s="9"/>
-      <x:c r="F48" s="9"/>
-      <x:c r="G48" s="9"/>
-      <x:c r="H48" s="9"/>
-      <x:c r="I48" s="9"/>
-      <x:c r="J48" s="9"/>
-      <x:c r="K48" s="10" t="s">
+      <x:c r="D51" s="11" t="s">
         <x:v>198</x:v>
       </x:c>
-    </x:row>
-    <x:row r="49" spans="1:11">
-      <x:c r="A49" s="4"/>
-      <x:c r="B49" s="4"/>
-      <x:c r="C49" s="4"/>
-      <x:c r="D49" s="4"/>
-      <x:c r="E49" s="4"/>
-      <x:c r="F49" s="4"/>
-      <x:c r="G49" s="4"/>
-      <x:c r="H49" s="4"/>
-      <x:c r="I49" s="4"/>
-      <x:c r="J49" s="4"/>
-      <x:c r="K49" s="4"/>
-    </x:row>
-    <x:row r="50" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A50" s="11" t="s">
+      <x:c r="E51" s="11" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="B50" s="11" t="s">
+      <x:c r="F51" s="11" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="C50" s="11" t="s">
+      <x:c r="G51" s="11" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="D50" s="11" t="s">
+      <x:c r="H51" s="11" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="E50" s="11" t="s">
+      <x:c r="I51" s="11" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F50" s="11" t="s">
+      <x:c r="J51" s="11" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G50" s="11" t="s">
+      <x:c r="K51" s="11" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H50" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="I50" s="11" t="s">
+    </x:row>
+    <x:row r="52" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A52" s="13" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="J50" s="11" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="K50" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A51" s="13" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B51" s="13" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="C51" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D51" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E51" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F51" s="13" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="G51" s="13" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="H51" s="13" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="I51" s="13" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="J51" s="13" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="K51" s="13" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:11">
-      <x:c r="A52" s="4"/>
-      <x:c r="B52" s="4"/>
-      <x:c r="C52" s="4"/>
-      <x:c r="D52" s="4"/>
-      <x:c r="E52" s="4"/>
-      <x:c r="F52" s="4"/>
-      <x:c r="G52" s="4"/>
-      <x:c r="H52" s="4"/>
-      <x:c r="I52" s="4"/>
-      <x:c r="J52" s="4"/>
-      <x:c r="K52" s="4"/>
-    </x:row>
-    <x:row r="53" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A53" s="8" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="B53" s="9"/>
-      <x:c r="C53" s="9"/>
-      <x:c r="D53" s="9"/>
-      <x:c r="E53" s="9"/>
-      <x:c r="F53" s="9"/>
-      <x:c r="G53" s="9"/>
-      <x:c r="H53" s="9"/>
-      <x:c r="I53" s="9"/>
-      <x:c r="J53" s="9"/>
-      <x:c r="K53" s="10" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:11">
-      <x:c r="A54" s="4"/>
-      <x:c r="B54" s="4"/>
-      <x:c r="C54" s="4"/>
-      <x:c r="D54" s="4"/>
-      <x:c r="E54" s="4"/>
-      <x:c r="F54" s="4"/>
-      <x:c r="G54" s="4"/>
-      <x:c r="H54" s="4"/>
-      <x:c r="I54" s="4"/>
-      <x:c r="J54" s="4"/>
-      <x:c r="K54" s="4"/>
-    </x:row>
-    <x:row r="55" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A55" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B55" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C55" s="11" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D55" s="11" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="E55" s="11" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F55" s="11" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G55" s="11" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H55" s="11" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="I55" s="11" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="J55" s="11" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="K55" s="11" t="s">
-        <x:v>223</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A56" s="13" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="B56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="C56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="E56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="I56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="J56" s="13" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="K56" s="13" t="s">
-        <x:v>225</x:v>
+      <x:c r="B52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="I52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="J52" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K52" s="13" t="s">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2722,9 +2533,9 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A32:F32"/>
-    <x:mergeCell ref="A48:J48"/>
-    <x:mergeCell ref="A53:J53"/>
+    <x:mergeCell ref="A28:F28"/>
+    <x:mergeCell ref="A44:J44"/>
+    <x:mergeCell ref="A49:J49"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 28/08/2026, 09:29</x:t>
+    <x:t>Conta: 6445064 | 31/08/2026, 17:20</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>52,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 27.132.847,50</x:t>
+    <x:t>R$ 27.144.378,62</x:t>
   </x:si>
   <x:si>
     <x:t>3,70%|Prefixada</x:t>
@@ -109,10 +109,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 378.406,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 366.645,17</x:t>
+    <x:t>R$ 378.580,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 366.793,38</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 255.651,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 247.303,58</x:t>
+    <x:t>R$ 255.775,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 247.409,46</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.600,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.060,00</x:t>
+    <x:t>R$ 313.741,06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.179,90</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.282,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.489,91</x:t>
+    <x:t>R$ 315.427,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.613,31</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -175,10 +175,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.160,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.536,21</x:t>
+    <x:t>R$ 314.302,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.657,28</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -190,10 +190,10 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 254.580,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.393,25</x:t>
+    <x:t>R$ 254.702,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.497,08</x:t>
   </x:si>
   <x:si>
     <x:t>46,80%|Pós-Fixada</x:t>
@@ -208,10 +208,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 270.433,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 259.868,44</x:t>
+    <x:t>R$ 270.596,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 260.007,38</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -235,7 +235,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.895.580,95</x:t>
+    <x:t>R$ 20.904.702,44</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -259,7 +259,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 938.467,38</x:t>
+    <x:t>R$ 938.860,08</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -277,7 +277,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.062,40</x:t>
+    <x:t>R$ 1.004.482,54</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.116.878,40</x:t>
+    <x:t>R$ 1.117.345,75</x:t>
   </x:si>
   <x:si>
     <x:t>1,80%|Inflação</x:t>
@@ -304,10 +304,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 434.830,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 422.106,31</x:t>
+    <x:t>R$ 434.878,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.146,98</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -319,10 +319,10 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 444.535,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 430.355,25</x:t>
+    <x:t>R$ 444.603,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 430.413,39</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -343,10 +343,10 @@
     <x:t>R$ 74.699,90</x:t>
   </x:si>
   <x:si>
-    <x:t>46,7%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 24.147.903,86</x:t>
+    <x:t>46,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 24.147.153,63</x:t>
   </x:si>
   <x:si>
     <x:t>46,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -367,76 +367,73 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 563,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>904,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 509.816,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 507.607,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.460,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.854.184,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.841.992,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>246.820,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 795.399,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 794.212,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
+  </x:si>
+  <x:si>
     <x:t>28/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 563,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>904,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 509.519,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 507.377,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.460,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.851.231,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.839.704,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>246.820,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 794.481,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 793.431,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26/08/2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>R$ 2,20</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 621.241,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 606.901,71</x:t>
+    <x:t>R$ 621.995,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 607.542,97</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
@@ -448,121 +445,121 @@
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 192.140,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 191.255,81</x:t>
+    <x:t>R$ 192.338,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 191.424,05</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.811.826,77</x:t>
+    <x:t>R$ 4.816.993,22</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.722.278,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.576.911,97</x:t>
+    <x:t>R$ 4.727.348,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.581.221,73</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,17</x:t>
+    <x:t>R$ 2,18</x:t>
   </x:si>
   <x:si>
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 275.057,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 265.423,38</x:t>
+    <x:t>R$ 275.372,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 265.690,80</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 198,54</x:t>
+    <x:t>R$ 198,75</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.015.463,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.714.032,39</x:t>
+    <x:t>R$ 6.021.859,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.719.469,53</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 186,77</x:t>
+    <x:t>R$ 186,17</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.855.566,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.823.659,80</x:t>
+    <x:t>R$ 5.836.693,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.807.617,78</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 158,77</x:t>
+    <x:t>R$ 158,85</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 93.943,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.162,66</x:t>
+    <x:t>R$ 93.991,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.199,63</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,72</x:t>
+    <x:t>R$ 2,73</x:t>
   </x:si>
   <x:si>
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 177.359,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 171.125,92</x:t>
+    <x:t>R$ 177.466,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 171.216,27</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,47</x:t>
+    <x:t>R$ 1,48</x:t>
   </x:si>
   <x:si>
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.039.621,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.030.706,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,93%|Fundos Imobiliários</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 482.004,80</x:t>
+    <x:t>R$ 2.040.688,85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.031.533,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,95%|Fundos Imobiliários</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 494.160,00</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -601,10 +598,10 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 17,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 84,86</x:t>
+    <x:t>-R$ 15,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 87,00</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -1239,10 +1236,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>51762756.1550205</x:v>
+        <x:v>51785692.247707</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>51762756.1550205</x:v>
+        <x:v>51785692.247707</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>
@@ -2010,22 +2007,22 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C32" s="12" t="s">
+      <x:c r="D32" s="12" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="D32" s="12" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="G32" s="12" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="H32" s="3"/>
       <x:c r="I32" s="3"/>
@@ -2034,25 +2031,25 @@
     </x:row>
     <x:row r="33" spans="1:11" ht="30" customHeight="1">
       <x:c r="A33" s="12" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B33" s="12" t="s">
+      <x:c r="C33" s="12" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C33" s="12" t="s">
+      <x:c r="D33" s="12" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="G33" s="12" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="H33" s="3"/>
       <x:c r="I33" s="3"/>
@@ -2061,25 +2058,25 @@
     </x:row>
     <x:row r="34" spans="1:11" ht="30" customHeight="1">
       <x:c r="A34" s="12" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B34" s="12" t="s">
+      <x:c r="C34" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="C34" s="12" t="s">
+      <x:c r="D34" s="12" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="G34" s="12" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="H34" s="3"/>
       <x:c r="I34" s="3"/>
@@ -2088,25 +2085,25 @@
     </x:row>
     <x:row r="35" spans="1:11" ht="30" customHeight="1">
       <x:c r="A35" s="12" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B35" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C35" s="12" t="s">
+      <x:c r="D35" s="12" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="G35" s="12" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="H35" s="3"/>
       <x:c r="I35" s="3"/>
@@ -2115,25 +2112,25 @@
     </x:row>
     <x:row r="36" spans="1:11" ht="30" customHeight="1">
       <x:c r="A36" s="12" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B36" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C36" s="12" t="s">
+      <x:c r="D36" s="12" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="G36" s="12" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2142,25 +2139,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B37" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C37" s="12" t="s">
+      <x:c r="D37" s="12" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="G37" s="12" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2169,25 +2166,25 @@
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
       <x:c r="A38" s="12" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B38" s="12" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C38" s="12" t="s">
+      <x:c r="D38" s="12" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="G38" s="12" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
       <x:c r="I38" s="3"/>
@@ -2196,25 +2193,25 @@
     </x:row>
     <x:row r="39" spans="1:11" ht="30" customHeight="1">
       <x:c r="A39" s="12" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B39" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C39" s="12" t="s">
+      <x:c r="D39" s="12" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="D39" s="12" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="G39" s="12" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="H39" s="3"/>
       <x:c r="I39" s="3"/>
@@ -2223,25 +2220,25 @@
     </x:row>
     <x:row r="40" spans="1:11" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="C40" s="12" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="s">
-        <x:v>168</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="G40" s="12" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="H40" s="3"/>
       <x:c r="I40" s="3"/>
@@ -2250,25 +2247,25 @@
     </x:row>
     <x:row r="41" spans="1:11" ht="30" customHeight="1">
       <x:c r="A41" s="12" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C41" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B41" s="12" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C41" s="12" t="s">
+      <x:c r="D41" s="12" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="D41" s="12" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="G41" s="12" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
@@ -2277,25 +2274,25 @@
     </x:row>
     <x:row r="42" spans="1:11" ht="30" customHeight="1">
       <x:c r="A42" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D42" s="13" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="D42" s="13" t="s">
-        <x:v>178</x:v>
       </x:c>
       <x:c r="E42" s="13" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F42" s="13" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="G42" s="13" t="s">
-        <x:v>180</x:v>
       </x:c>
       <x:c r="H42" s="3"/>
       <x:c r="I42" s="3"/>
@@ -2317,7 +2314,7 @@
     </x:row>
     <x:row r="44" spans="1:11" ht="45" customHeight="1">
       <x:c r="A44" s="8" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B44" s="9"/>
       <x:c r="C44" s="9"/>
@@ -2329,7 +2326,7 @@
       <x:c r="I44" s="9"/>
       <x:c r="J44" s="9"/>
       <x:c r="K44" s="10" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2347,34 +2344,34 @@
     </x:row>
     <x:row r="46" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A46" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B46" s="11" t="s">
+      <x:c r="C46" s="11" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C46" s="11" t="s">
+      <x:c r="D46" s="11" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D46" s="11" t="s">
+      <x:c r="E46" s="11" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="E46" s="11" t="s">
+      <x:c r="F46" s="11" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="s">
+      <x:c r="G46" s="11" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G46" s="11" t="s">
+      <x:c r="H46" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H46" s="11" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="I46" s="11" t="s">
+      <x:c r="J46" s="11" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="J46" s="11" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="K46" s="11" t="s">
         <x:v>16</x:v>
@@ -2382,10 +2379,10 @@
     </x:row>
     <x:row r="47" spans="1:11" ht="30" customHeight="1">
       <x:c r="A47" s="13" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B47" s="13" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="B47" s="13" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="C47" s="13" t="s">
         <x:v>23</x:v>
@@ -2397,22 +2394,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F47" s="13" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G47" s="13" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G47" s="13" t="s">
+      <x:c r="H47" s="13" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="I47" s="13" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H47" s="13" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="I47" s="13" t="s">
+      <x:c r="J47" s="13" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="J47" s="13" t="s">
-        <x:v>196</x:v>
-      </x:c>
       <x:c r="K47" s="13" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2466,66 +2463,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="11" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D51" s="11" t="s">
+      <x:c r="E51" s="11" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="E51" s="11" t="s">
+      <x:c r="F51" s="11" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="F51" s="11" t="s">
+      <x:c r="G51" s="11" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G51" s="11" t="s">
+      <x:c r="H51" s="11" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="H51" s="11" t="s">
+      <x:c r="I51" s="11" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="I51" s="11" t="s">
+      <x:c r="J51" s="11" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="J51" s="11" t="s">
+      <x:c r="K51" s="11" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="K51" s="11" t="s">
-        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11" ht="30" customHeight="1">
       <x:c r="A52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="I52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="J52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K52" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 31/08/2026, 17:20</x:t>
+    <x:t>Conta: 6445064 | 04/09/2026, 14:13</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,10 +34,10 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>52,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 27.144.378,62</x:t>
+    <x:t>52,5%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 27.190.553,38</x:t>
   </x:si>
   <x:si>
     <x:t>3,70%|Prefixada</x:t>
@@ -109,10 +109,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 378.580,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 366.793,38</x:t>
+    <x:t>R$ 379.278,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 367.386,91</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 255.775,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 247.409,46</x:t>
+    <x:t>R$ 256.274,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 247.833,47</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.741,06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.179,90</x:t>
+    <x:t>R$ 314.305,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 304.660,06</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.427,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.613,31</x:t>
+    <x:t>R$ 316.008,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.107,45</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -175,10 +175,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.302,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.657,28</x:t>
+    <x:t>R$ 314.873,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.142,08</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -190,10 +190,10 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 254.702,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.497,08</x:t>
+    <x:t>R$ 255.191,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246.912,91</x:t>
   </x:si>
   <x:si>
     <x:t>46,80%|Pós-Fixada</x:t>
@@ -208,10 +208,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 270.596,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 260.007,38</x:t>
+    <x:t>R$ 271.251,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 260.563,97</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -235,7 +235,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.904.702,44</x:t>
+    <x:t>R$ 20.941.228,21</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -259,7 +259,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 938.860,08</x:t>
+    <x:t>R$ 940.432,51</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -277,7 +277,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.482,54</x:t>
+    <x:t>R$ 1.006.164,89</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.117.345,75</x:t>
+    <x:t>R$ 1.119.217,12</x:t>
   </x:si>
   <x:si>
     <x:t>1,80%|Inflação</x:t>
@@ -304,10 +304,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 434.878,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 422.146,98</x:t>
+    <x:t>R$ 435.070,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.309,72</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -319,10 +319,10 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 444.603,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 430.413,39</x:t>
+    <x:t>R$ 444.877,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 430.646,00</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -346,7 +346,7 @@
     <x:t>46,6%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 24.147.153,63</x:t>
+    <x:t>R$ 24.164.391,53</x:t>
   </x:si>
   <x:si>
     <x:t>46,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -367,10 +367,10 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 563,52</x:t>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 564,69</x:t>
   </x:si>
   <x:si>
     <x:t>904,71</x:t>
@@ -379,31 +379,31 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 509.816,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 507.607,65</x:t>
+    <x:t>R$ 510.882,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 508.433,80</x:t>
   </x:si>
   <x:si>
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 272,86</x:t>
+    <x:t>R$ 273,42</x:t>
   </x:si>
   <x:si>
     <x:t>10.460,17</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.854.184,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.841.992,71</x:t>
+    <x:t>R$ 2.859.992,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.846.494,54</x:t>
   </x:si>
   <x:si>
     <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>27/08/2026</x:t>
+    <x:t>28/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 3,22</x:t>
@@ -412,16 +412,16 @@
     <x:t>246.820,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 795.399,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 794.212,09</x:t>
+    <x:t>R$ 795.706,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 794.473,16</x:t>
   </x:si>
   <x:si>
     <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>28/08/2026</x:t>
+    <x:t>02/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2,20</x:t>
@@ -430,40 +430,43 @@
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 621.995,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 607.542,97</x:t>
+    <x:t>R$ 623.015,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 608.410,07</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,91</x:t>
+    <x:t>03/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,92</x:t>
   </x:si>
   <x:si>
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 192.338,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 191.424,05</x:t>
+    <x:t>R$ 192.949,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 191.944,08</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.816.993,22</x:t>
+    <x:t>R$ 4.825.214,25</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.727.348,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.581.221,73</x:t>
+    <x:t>R$ 4.735.416,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.588.079,56</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
@@ -475,55 +478,55 @@
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 275.372,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 265.690,80</x:t>
+    <x:t>R$ 276.008,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 266.231,67</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 198,75</x:t>
+    <x:t>R$ 199,58</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.021.859,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.719.469,53</x:t>
+    <x:t>R$ 6.046.815,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.740.681,57</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 186,17</x:t>
+    <x:t>R$ 185,21</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.836.693,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.807.617,78</x:t>
+    <x:t>R$ 5.806.470,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.781.928,29</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 158,85</x:t>
+    <x:t>R$ 159,17</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 93.991,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.199,63</x:t>
+    <x:t>R$ 94.181,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.347,09</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
@@ -535,10 +538,10 @@
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 177.466,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 171.216,27</x:t>
+    <x:t>R$ 177.896,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 171.582,50</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -550,16 +553,16 @@
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.040.688,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.031.533,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,95%|Fundos Imobiliários</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 494.160,00</x:t>
+    <x:t>R$ 2.045.054,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.034.917,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,93%|Fundos Imobiliários</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 482.800,00</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -598,10 +601,34 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 15,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 87,00</x:t>
+    <x:t>-R$ 17,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 85,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Proventos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.840,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Indexador</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data Provisão Pagamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quantidade Provisionada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provisionado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENDIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -1176,7 +1203,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K52"/>
+  <x:dimension ref="A1:K57"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="51.853482" style="0" customWidth="1"/>
@@ -1236,10 +1263,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>51785692.247707</x:v>
+        <x:v>51840584.9106885</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>51785692.247707</x:v>
+        <x:v>51840584.9106885</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>
@@ -2088,22 +2115,22 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C35" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G35" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H35" s="3"/>
       <x:c r="I35" s="3"/>
@@ -2112,25 +2139,25 @@
     </x:row>
     <x:row r="36" spans="1:11" ht="30" customHeight="1">
       <x:c r="A36" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="C36" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G36" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2139,25 +2166,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C37" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G37" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2166,25 +2193,25 @@
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
       <x:c r="A38" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C38" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G38" s="12" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
       <x:c r="I38" s="3"/>
@@ -2193,25 +2220,25 @@
     </x:row>
     <x:row r="39" spans="1:11" ht="30" customHeight="1">
       <x:c r="A39" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C39" s="12" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G39" s="12" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H39" s="3"/>
       <x:c r="I39" s="3"/>
@@ -2220,25 +2247,25 @@
     </x:row>
     <x:row r="40" spans="1:11" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="C40" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G40" s="12" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H40" s="3"/>
       <x:c r="I40" s="3"/>
@@ -2247,25 +2274,25 @@
     </x:row>
     <x:row r="41" spans="1:11" ht="30" customHeight="1">
       <x:c r="A41" s="12" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C41" s="12" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G41" s="12" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
@@ -2274,25 +2301,25 @@
     </x:row>
     <x:row r="42" spans="1:11" ht="30" customHeight="1">
       <x:c r="A42" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D42" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E42" s="13" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F42" s="13" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G42" s="13" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H42" s="3"/>
       <x:c r="I42" s="3"/>
@@ -2314,7 +2341,7 @@
     </x:row>
     <x:row r="44" spans="1:11" ht="45" customHeight="1">
       <x:c r="A44" s="8" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B44" s="9"/>
       <x:c r="C44" s="9"/>
@@ -2326,7 +2353,7 @@
       <x:c r="I44" s="9"/>
       <x:c r="J44" s="9"/>
       <x:c r="K44" s="10" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2344,34 +2371,34 @@
     </x:row>
     <x:row r="46" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A46" s="11" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B46" s="11" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C46" s="11" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D46" s="11" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E46" s="11" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F46" s="11" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G46" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H46" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="I46" s="11" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J46" s="11" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K46" s="11" t="s">
         <x:v>16</x:v>
@@ -2379,10 +2406,10 @@
     </x:row>
     <x:row r="47" spans="1:11" ht="30" customHeight="1">
       <x:c r="A47" s="13" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B47" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C47" s="13" t="s">
         <x:v>23</x:v>
@@ -2394,22 +2421,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F47" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G47" s="13" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H47" s="13" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="I47" s="13" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="J47" s="13" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K47" s="13" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2427,20 +2454,20 @@
     </x:row>
     <x:row r="49" spans="1:11" ht="45" customHeight="1">
       <x:c r="A49" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B49" s="9"/>
       <x:c r="C49" s="9"/>
       <x:c r="D49" s="9"/>
       <x:c r="E49" s="9"/>
       <x:c r="F49" s="9"/>
-      <x:c r="G49" s="9"/>
-      <x:c r="H49" s="9"/>
-      <x:c r="I49" s="9"/>
-      <x:c r="J49" s="9"/>
-      <x:c r="K49" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="G49" s="10" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H49" s="3"/>
+      <x:c r="I49" s="3"/>
+      <x:c r="J49" s="3"/>
+      <x:c r="K49" s="3"/>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="4"/>
@@ -2450,89 +2477,179 @@
       <x:c r="E50" s="4"/>
       <x:c r="F50" s="4"/>
       <x:c r="G50" s="4"/>
-      <x:c r="H50" s="4"/>
-      <x:c r="I50" s="4"/>
-      <x:c r="J50" s="4"/>
-      <x:c r="K50" s="4"/>
+      <x:c r="H50" s="3"/>
+      <x:c r="I50" s="3"/>
+      <x:c r="J50" s="3"/>
+      <x:c r="K50" s="3"/>
     </x:row>
     <x:row r="51" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A51" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B51" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C51" s="11" t="s">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D51" s="11" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E51" s="11" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F51" s="11" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G51" s="11" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H51" s="11" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="I51" s="11" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="J51" s="11" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="K51" s="11" t="s">
-        <x:v>204</x:v>
-      </x:c>
+      <x:c r="F51" s="3"/>
+      <x:c r="G51" s="3"/>
+      <x:c r="H51" s="3"/>
+      <x:c r="I51" s="3"/>
+      <x:c r="J51" s="3"/>
+      <x:c r="K51" s="3"/>
     </x:row>
     <x:row r="52" spans="1:11" ht="30" customHeight="1">
       <x:c r="A52" s="13" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D52" s="13" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F52" s="3"/>
+      <x:c r="G52" s="3"/>
+      <x:c r="H52" s="3"/>
+      <x:c r="I52" s="3"/>
+      <x:c r="J52" s="3"/>
+      <x:c r="K52" s="3"/>
+    </x:row>
+    <x:row r="53" spans="1:11">
+      <x:c r="A53" s="4"/>
+      <x:c r="B53" s="4"/>
+      <x:c r="C53" s="4"/>
+      <x:c r="D53" s="4"/>
+      <x:c r="E53" s="4"/>
+      <x:c r="F53" s="4"/>
+      <x:c r="G53" s="4"/>
+      <x:c r="H53" s="4"/>
+      <x:c r="I53" s="4"/>
+      <x:c r="J53" s="4"/>
+      <x:c r="K53" s="4"/>
+    </x:row>
+    <x:row r="54" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A54" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B54" s="9"/>
+      <x:c r="C54" s="9"/>
+      <x:c r="D54" s="9"/>
+      <x:c r="E54" s="9"/>
+      <x:c r="F54" s="9"/>
+      <x:c r="G54" s="9"/>
+      <x:c r="H54" s="9"/>
+      <x:c r="I54" s="9"/>
+      <x:c r="J54" s="9"/>
+      <x:c r="K54" s="10" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:11">
+      <x:c r="A55" s="4"/>
+      <x:c r="B55" s="4"/>
+      <x:c r="C55" s="4"/>
+      <x:c r="D55" s="4"/>
+      <x:c r="E55" s="4"/>
+      <x:c r="F55" s="4"/>
+      <x:c r="G55" s="4"/>
+      <x:c r="H55" s="4"/>
+      <x:c r="I55" s="4"/>
+      <x:c r="J55" s="4"/>
+      <x:c r="K55" s="4"/>
+    </x:row>
+    <x:row r="56" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A56" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B56" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="B52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="I52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="J52" s="13" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="K52" s="13" t="s">
-        <x:v>205</x:v>
+      <x:c r="D56" s="11" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G56" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H56" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="I56" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="J56" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K56" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="I57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="J57" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K57" s="13" t="s">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A28:F28"/>
     <x:mergeCell ref="A44:J44"/>
-    <x:mergeCell ref="A49:J49"/>
+    <x:mergeCell ref="A49:F49"/>
+    <x:mergeCell ref="A54:J54"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
